--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_validation_results.xlsx
@@ -33956,10 +33956,10 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
@@ -33998,7 +33998,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>175.2130737999687</v>
+        <v>250.310899599921</v>
       </c>
       <c r="B2" t="n">
         <v>180</v>
@@ -34007,7 +34007,7 @@
         <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>3.081961571310829</v>
+        <v>2.157317010417098</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_validation_results.xlsx
@@ -29396,7 +29396,7 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
@@ -29563,7 +29563,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -29640,7 +29640,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -29794,7 +29794,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -29871,7 +29871,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -29948,7 +29948,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -30102,7 +30102,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -30179,7 +30179,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -30410,7 +30410,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -30487,7 +30487,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>family_and_node_action_candidate</t>
+          <t>process_guard_admitted</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -30718,7 +30718,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -31103,7 +31103,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>family_and_node_action_candidate</t>
+          <t>process_guard_admitted</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -31334,7 +31334,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -31488,7 +31488,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -31642,7 +31642,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -31719,7 +31719,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -31950,7 +31950,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -32027,7 +32027,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -32104,7 +32104,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -32258,7 +32258,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -32335,7 +32335,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -32412,7 +32412,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -32566,7 +32566,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -32643,7 +32643,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -32720,7 +32720,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -32874,7 +32874,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -32951,7 +32951,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>family_and_node_action_candidate</t>
+          <t>process_guard_admitted</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -33028,7 +33028,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -33182,7 +33182,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -33259,7 +33259,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -33490,7 +33490,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -33644,7 +33644,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>scientific_score_ready</t>
+          <t>scientific_score_admitted</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -33998,7 +33998,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>250.310899599921</v>
+        <v>241.7737677999539</v>
       </c>
       <c r="B2" t="n">
         <v>180</v>
@@ -34007,7 +34007,7 @@
         <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>2.157317010417098</v>
+        <v>2.233492806525334</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_validation_results.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="acceptance" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'injection_trials'!$A$1:$U$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'injection_trials'!$A$1:$Z$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'negative_controls'!$A$1:$I$361</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'metrics_by_scenario'!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'regime_hysteresis'!$A$1:$H$2</definedName>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U181"/>
+  <dimension ref="A1:Z181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -467,8 +467,13 @@
     <col width="23" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="38" customWidth="1" min="20" max="20"/>
-    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,10 +574,35 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>top2_hit</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>reciprocal_rank</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_sensor</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_analyte</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>topological_hop_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>localization_statistic</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>max_affected_localization_delta</t>
         </is>
@@ -654,12 +684,31 @@
       <c r="S2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="Z2" t="n">
         <v>0.09123472874593094</v>
       </c>
     </row>
@@ -739,12 +788,31 @@
       <c r="S3" t="b">
         <v>1</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="Z3" t="n">
         <v>0.2285508833020156</v>
       </c>
     </row>
@@ -824,12 +892,31 @@
       <c r="S4" t="b">
         <v>0</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="Z4" t="n">
         <v>-0.1842945911919267</v>
       </c>
     </row>
@@ -909,12 +996,31 @@
       <c r="S5" t="b">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="Z5" t="n">
         <v>0.2245058582870594</v>
       </c>
     </row>
@@ -994,12 +1100,31 @@
       <c r="S6" t="b">
         <v>1</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="Z6" t="n">
         <v>0.2484423046344471</v>
       </c>
     </row>
@@ -1079,12 +1204,31 @@
       <c r="S7" t="b">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="Z7" t="n">
         <v>0.139745139336141</v>
       </c>
     </row>
@@ -1164,12 +1308,31 @@
       <c r="S8" t="b">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="Z8" t="n">
         <v>0.5522555535716739</v>
       </c>
     </row>
@@ -1249,12 +1412,31 @@
       <c r="S9" t="b">
         <v>1</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="Z9" t="n">
         <v>0.272182490499874</v>
       </c>
     </row>
@@ -1334,12 +1516,31 @@
       <c r="S10" t="b">
         <v>1</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="Z10" t="n">
         <v>0.8254004221042776</v>
       </c>
     </row>
@@ -1419,12 +1620,31 @@
       <c r="S11" t="b">
         <v>1</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="Z11" t="n">
         <v>0.77444408354592</v>
       </c>
     </row>
@@ -1504,12 +1724,31 @@
       <c r="S12" t="b">
         <v>1</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="Z12" t="n">
         <v>0.8702072113247752</v>
       </c>
     </row>
@@ -1589,12 +1828,31 @@
       <c r="S13" t="b">
         <v>0</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="Z13" t="n">
         <v>0.190499830174277</v>
       </c>
     </row>
@@ -1674,12 +1932,31 @@
       <c r="S14" t="b">
         <v>1</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="Z14" t="n">
         <v>0.8797279816064761</v>
       </c>
     </row>
@@ -1759,12 +2036,31 @@
       <c r="S15" t="b">
         <v>1</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="Z15" t="n">
         <v>0.1408669043538243</v>
       </c>
     </row>
@@ -1844,12 +2140,31 @@
       <c r="S16" t="b">
         <v>1</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="Z16" t="n">
         <v>0.9052910175360758</v>
       </c>
     </row>
@@ -1929,12 +2244,31 @@
       <c r="S17" t="b">
         <v>1</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="Z17" t="n">
         <v>0.1547820090821679</v>
       </c>
     </row>
@@ -2014,12 +2348,31 @@
       <c r="S18" t="b">
         <v>1</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U18" t="n">
+      <c r="Z18" t="n">
         <v>0.1719327436046523</v>
       </c>
     </row>
@@ -2099,12 +2452,31 @@
       <c r="S19" t="b">
         <v>0</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U19" t="n">
+      <c r="Z19" t="n">
         <v>0.04026794181961946</v>
       </c>
     </row>
@@ -2184,12 +2556,31 @@
       <c r="S20" t="b">
         <v>1</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U20" t="n">
+      <c r="Z20" t="n">
         <v>0.7049042332023376</v>
       </c>
     </row>
@@ -2269,12 +2660,31 @@
       <c r="S21" t="b">
         <v>1</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="Z21" t="n">
         <v>0.4713970887006663</v>
       </c>
     </row>
@@ -2354,12 +2764,31 @@
       <c r="S22" t="b">
         <v>1</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U22" t="n">
+      <c r="Z22" t="n">
         <v>0.7678757470973959</v>
       </c>
     </row>
@@ -2439,12 +2868,31 @@
       <c r="S23" t="b">
         <v>1</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T23" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="Z23" t="n">
         <v>0.4404962018060713</v>
       </c>
     </row>
@@ -2524,12 +2972,31 @@
       <c r="S24" t="b">
         <v>1</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U24" t="n">
+      <c r="Z24" t="n">
         <v>0.8347572275767673</v>
       </c>
     </row>
@@ -2609,12 +3076,31 @@
       <c r="S25" t="b">
         <v>0</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U25" t="n">
+      <c r="Z25" t="n">
         <v>0.1365028627293801</v>
       </c>
     </row>
@@ -2694,12 +3180,31 @@
       <c r="S26" t="b">
         <v>1</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U26" t="n">
+      <c r="Z26" t="n">
         <v>0.8271539520073533</v>
       </c>
     </row>
@@ -2779,12 +3284,31 @@
       <c r="S27" t="b">
         <v>1</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U27" t="n">
+      <c r="Z27" t="n">
         <v>0.2087650698489183</v>
       </c>
     </row>
@@ -2864,12 +3388,31 @@
       <c r="S28" t="b">
         <v>1</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="Z28" t="n">
         <v>0.8966438741078004</v>
       </c>
     </row>
@@ -2949,12 +3492,31 @@
       <c r="S29" t="b">
         <v>0</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U29" t="n">
+      <c r="Z29" t="n">
         <v>0.1945347281301065</v>
       </c>
     </row>
@@ -3034,12 +3596,31 @@
       <c r="S30" t="b">
         <v>1</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T30" t="b">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U30" t="n">
+      <c r="Z30" t="n">
         <v>0.8454649057938454</v>
       </c>
     </row>
@@ -3119,12 +3700,31 @@
       <c r="S31" t="b">
         <v>0</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U31" t="n">
+      <c r="Z31" t="n">
         <v>0.07311685085374275</v>
       </c>
     </row>
@@ -3204,12 +3804,31 @@
       <c r="S32" t="b">
         <v>1</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T32" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U32" t="n">
+      <c r="Z32" t="n">
         <v>0.8215270122144365</v>
       </c>
     </row>
@@ -3289,12 +3908,31 @@
       <c r="S33" t="b">
         <v>1</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U33" t="n">
+      <c r="Z33" t="n">
         <v>0.3393034056179536</v>
       </c>
     </row>
@@ -3374,12 +4012,31 @@
       <c r="S34" t="b">
         <v>1</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U34" t="n">
+      <c r="Z34" t="n">
         <v>0.8706740894405735</v>
       </c>
     </row>
@@ -3459,12 +4116,31 @@
       <c r="S35" t="b">
         <v>1</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T35" t="b">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U35" t="n">
+      <c r="Z35" t="n">
         <v>0.3877797259192217</v>
       </c>
     </row>
@@ -3544,12 +4220,31 @@
       <c r="S36" t="b">
         <v>1</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="T36" t="b">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U36" t="n">
+      <c r="Z36" t="n">
         <v>0.4741051912917433</v>
       </c>
     </row>
@@ -3629,12 +4324,31 @@
       <c r="S37" t="b">
         <v>1</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T37" t="b">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U37" t="n">
+      <c r="Z37" t="n">
         <v>0.3622543919543518</v>
       </c>
     </row>
@@ -3714,12 +4428,31 @@
       <c r="S38" t="b">
         <v>0</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U38" t="n">
+      <c r="Z38" t="n">
         <v>-0.03629700234941158</v>
       </c>
     </row>
@@ -3799,12 +4532,31 @@
       <c r="S39" t="b">
         <v>1</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U39" t="n">
+      <c r="Z39" t="n">
         <v>0.1407415583145802</v>
       </c>
     </row>
@@ -3884,12 +4636,31 @@
       <c r="S40" t="b">
         <v>1</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="T40" t="b">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U40" t="n">
+      <c r="Z40" t="n">
         <v>0.8519680604035005</v>
       </c>
     </row>
@@ -3969,12 +4740,31 @@
       <c r="S41" t="b">
         <v>0</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T41" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U41" t="n">
+      <c r="Z41" t="n">
         <v>-0.01476292679323754</v>
       </c>
     </row>
@@ -4054,12 +4844,31 @@
       <c r="S42" t="b">
         <v>1</v>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T42" t="b">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U42" t="n">
+      <c r="Z42" t="n">
         <v>0.5462542065610367</v>
       </c>
     </row>
@@ -4139,12 +4948,31 @@
       <c r="S43" t="b">
         <v>0</v>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T43" t="b">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U43" t="n">
+      <c r="Z43" t="n">
         <v>0.1506301524151367</v>
       </c>
     </row>
@@ -4224,12 +5052,31 @@
       <c r="S44" t="b">
         <v>1</v>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U44" t="n">
+      <c r="Z44" t="n">
         <v>0.9259488446953651</v>
       </c>
     </row>
@@ -4309,12 +5156,31 @@
       <c r="S45" t="b">
         <v>1</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T45" t="b">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U45" t="n">
+      <c r="Z45" t="n">
         <v>0.2082565565209921</v>
       </c>
     </row>
@@ -4394,12 +5260,31 @@
       <c r="S46" t="b">
         <v>1</v>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T46" t="b">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U46" t="n">
+      <c r="Z46" t="n">
         <v>0.6878125301333717</v>
       </c>
     </row>
@@ -4479,12 +5364,31 @@
       <c r="S47" t="b">
         <v>1</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="T47" t="b">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U47" t="n">
+      <c r="Z47" t="n">
         <v>0.2651287175437052</v>
       </c>
     </row>
@@ -4564,12 +5468,31 @@
       <c r="S48" t="b">
         <v>1</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T48" t="b">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U48" t="n">
+      <c r="Z48" t="n">
         <v>0.5134038570477792</v>
       </c>
     </row>
@@ -4649,12 +5572,31 @@
       <c r="S49" t="b">
         <v>0</v>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="T49" t="b">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U49" t="n">
+      <c r="Z49" t="n">
         <v>0.3407574393994217</v>
       </c>
     </row>
@@ -4734,12 +5676,31 @@
       <c r="S50" t="b">
         <v>1</v>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T50" t="b">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U50" t="n">
+      <c r="Z50" t="n">
         <v>0.1456667803935391</v>
       </c>
     </row>
@@ -4819,12 +5780,31 @@
       <c r="S51" t="b">
         <v>1</v>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T51" t="b">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U51" t="n">
+      <c r="Z51" t="n">
         <v>0.1665776182797234</v>
       </c>
     </row>
@@ -4904,12 +5884,31 @@
       <c r="S52" t="b">
         <v>1</v>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T52" t="b">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U52" t="n">
+      <c r="Z52" t="n">
         <v>0.9768629278980576</v>
       </c>
     </row>
@@ -4989,12 +5988,31 @@
       <c r="S53" t="b">
         <v>0</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U53" t="n">
+      <c r="Z53" t="n">
         <v>0.09016249755360162</v>
       </c>
     </row>
@@ -5074,12 +6092,31 @@
       <c r="S54" t="b">
         <v>0</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="T54" t="b">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U54" t="n">
+      <c r="Z54" t="n">
         <v>0.1145016039061699</v>
       </c>
     </row>
@@ -5159,12 +6196,31 @@
       <c r="S55" t="b">
         <v>0</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U55" t="n">
+      <c r="Z55" t="n">
         <v>0.02257422046770419</v>
       </c>
     </row>
@@ -5244,12 +6300,31 @@
       <c r="S56" t="b">
         <v>1</v>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T56" t="b">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U56" t="n">
+      <c r="Z56" t="n">
         <v>0.9108740600830629</v>
       </c>
     </row>
@@ -5329,12 +6404,31 @@
       <c r="S57" t="b">
         <v>1</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="T57" t="b">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U57" t="n">
+      <c r="Z57" t="n">
         <v>0.2661533734624472</v>
       </c>
     </row>
@@ -5414,12 +6508,31 @@
       <c r="S58" t="b">
         <v>1</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T58" t="b">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U58" t="n">
+      <c r="Z58" t="n">
         <v>0.8177761249256035</v>
       </c>
     </row>
@@ -5499,12 +6612,31 @@
       <c r="S59" t="b">
         <v>1</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="T59" t="b">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U59" t="n">
+      <c r="Z59" t="n">
         <v>0.8370986157136795</v>
       </c>
     </row>
@@ -5584,12 +6716,31 @@
       <c r="S60" t="b">
         <v>1</v>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T60" t="b">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U60" t="n">
+      <c r="Z60" t="n">
         <v>0.280806592052089</v>
       </c>
     </row>
@@ -5669,12 +6820,31 @@
       <c r="S61" t="b">
         <v>0</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T61" t="b">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U61" t="n">
+      <c r="Z61" t="n">
         <v>0.121941914166006</v>
       </c>
     </row>
@@ -5754,12 +6924,31 @@
       <c r="S62" t="b">
         <v>1</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="T62" t="b">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U62" t="n">
+      <c r="Z62" t="n">
         <v>0.2038892003680143</v>
       </c>
     </row>
@@ -5839,12 +7028,31 @@
       <c r="S63" t="b">
         <v>1</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="T63" t="b">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U63" t="n">
+      <c r="Z63" t="n">
         <v>0.2274483038895692</v>
       </c>
     </row>
@@ -5924,12 +7132,31 @@
       <c r="S64" t="b">
         <v>0</v>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="T64" t="b">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U64" t="n">
+      <c r="Z64" t="n">
         <v>0.02405152651189135</v>
       </c>
     </row>
@@ -6009,12 +7236,31 @@
       <c r="S65" t="b">
         <v>0</v>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="T65" t="b">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U65" t="n">
+      <c r="Z65" t="n">
         <v>0.1995393110177656</v>
       </c>
     </row>
@@ -6094,12 +7340,31 @@
       <c r="S66" t="b">
         <v>1</v>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="T66" t="b">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U66" t="n">
+      <c r="Z66" t="n">
         <v>0.2372663930250213</v>
       </c>
     </row>
@@ -6179,12 +7444,31 @@
       <c r="S67" t="b">
         <v>0</v>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T67" t="b">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U67" t="n">
+      <c r="Z67" t="n">
         <v>-0.1288906832133828</v>
       </c>
     </row>
@@ -6264,12 +7548,31 @@
       <c r="S68" t="b">
         <v>0</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="T68" t="b">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U68" t="n">
+      <c r="Z68" t="n">
         <v>0.5474016236110527</v>
       </c>
     </row>
@@ -6349,12 +7652,31 @@
       <c r="S69" t="b">
         <v>0</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="T69" t="b">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U69" t="n">
+      <c r="Z69" t="n">
         <v>0.1934181144271703</v>
       </c>
     </row>
@@ -6434,12 +7756,31 @@
       <c r="S70" t="b">
         <v>1</v>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="T70" t="b">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U70" t="n">
+      <c r="Z70" t="n">
         <v>0.8503059796657415</v>
       </c>
     </row>
@@ -6519,12 +7860,31 @@
       <c r="S71" t="b">
         <v>1</v>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="T71" t="b">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U71" t="n">
+      <c r="Z71" t="n">
         <v>0.7266677258881729</v>
       </c>
     </row>
@@ -6604,12 +7964,31 @@
       <c r="S72" t="b">
         <v>1</v>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="T72" t="b">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U72" t="n">
+      <c r="Z72" t="n">
         <v>0.8716973597189805</v>
       </c>
     </row>
@@ -6689,12 +8068,31 @@
       <c r="S73" t="b">
         <v>1</v>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="T73" t="b">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U73" t="n">
+      <c r="Z73" t="n">
         <v>0.05650446318261615</v>
       </c>
     </row>
@@ -6774,12 +8172,31 @@
       <c r="S74" t="b">
         <v>0</v>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="T74" t="b">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U74" t="n">
+      <c r="Z74" t="n">
         <v>0.323091945283039</v>
       </c>
     </row>
@@ -6859,12 +8276,31 @@
       <c r="S75" t="b">
         <v>1</v>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="T75" t="b">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U75" t="n">
+      <c r="Z75" t="n">
         <v>0.0657368195921888</v>
       </c>
     </row>
@@ -6944,12 +8380,31 @@
       <c r="S76" t="b">
         <v>1</v>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T76" t="b">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U76" t="n">
+      <c r="Z76" t="n">
         <v>0.9409390645408521</v>
       </c>
     </row>
@@ -7029,12 +8484,31 @@
       <c r="S77" t="b">
         <v>0</v>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="T77" t="b">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U77" t="n">
+      <c r="Z77" t="n">
         <v>-0.2689778339916523</v>
       </c>
     </row>
@@ -7114,12 +8588,31 @@
       <c r="S78" t="b">
         <v>1</v>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="T78" t="b">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U78" t="n">
+      <c r="Z78" t="n">
         <v>0.1738885204381463</v>
       </c>
     </row>
@@ -7199,12 +8692,31 @@
       <c r="S79" t="b">
         <v>0</v>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="T79" t="b">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U79" t="n">
+      <c r="Z79" t="n">
         <v>-0.1066453092118932</v>
       </c>
     </row>
@@ -7284,12 +8796,31 @@
       <c r="S80" t="b">
         <v>1</v>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="T80" t="b">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U80" t="n">
+      <c r="Z80" t="n">
         <v>0.01873895548216613</v>
       </c>
     </row>
@@ -7369,12 +8900,31 @@
       <c r="S81" t="b">
         <v>0</v>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="T81" t="b">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U81" t="n">
+      <c r="Z81" t="n">
         <v>0.2556445588446121</v>
       </c>
     </row>
@@ -7454,12 +9004,31 @@
       <c r="S82" t="b">
         <v>1</v>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="T82" t="b">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U82" t="n">
+      <c r="Z82" t="n">
         <v>0.8425980013062707</v>
       </c>
     </row>
@@ -7539,12 +9108,31 @@
       <c r="S83" t="b">
         <v>0</v>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="T83" t="b">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U83" t="n">
+      <c r="Z83" t="n">
         <v>0.281325271461915</v>
       </c>
     </row>
@@ -7624,12 +9212,31 @@
       <c r="S84" t="b">
         <v>1</v>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="T84" t="b">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U84" t="n">
+      <c r="Z84" t="n">
         <v>0.8349287258111217</v>
       </c>
     </row>
@@ -7709,12 +9316,31 @@
       <c r="S85" t="b">
         <v>0</v>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="T85" t="b">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U85" t="n">
+      <c r="Z85" t="n">
         <v>-0.01660435368854385</v>
       </c>
     </row>
@@ -7794,12 +9420,31 @@
       <c r="S86" t="b">
         <v>0</v>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T86" t="b">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U86" t="n">
+      <c r="Z86" t="n">
         <v>0.29728174679654</v>
       </c>
     </row>
@@ -7879,12 +9524,31 @@
       <c r="S87" t="b">
         <v>0</v>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="T87" t="b">
+        <v>1</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y87" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U87" t="n">
+      <c r="Z87" t="n">
         <v>0.01035510450508326</v>
       </c>
     </row>
@@ -7964,12 +9628,31 @@
       <c r="S88" t="b">
         <v>1</v>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="T88" t="b">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U88" t="n">
+      <c r="Z88" t="n">
         <v>0.8108304107729324</v>
       </c>
     </row>
@@ -8049,12 +9732,31 @@
       <c r="S89" t="b">
         <v>0</v>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="T89" t="b">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y89" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U89" t="n">
+      <c r="Z89" t="n">
         <v>-0.4251785167631991</v>
       </c>
     </row>
@@ -8134,12 +9836,31 @@
       <c r="S90" t="b">
         <v>1</v>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="T90" t="b">
+        <v>1</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U90" t="n">
+      <c r="Z90" t="n">
         <v>0.4970759351449025</v>
       </c>
     </row>
@@ -8219,12 +9940,31 @@
       <c r="S91" t="b">
         <v>0</v>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="T91" t="b">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U91" t="n">
+      <c r="Z91" t="n">
         <v>-0.3031232849119455</v>
       </c>
     </row>
@@ -8304,12 +10044,31 @@
       <c r="S92" t="b">
         <v>1</v>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="T92" t="b">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U92" t="n">
+      <c r="Z92" t="n">
         <v>0.8295556607283504</v>
       </c>
     </row>
@@ -8389,12 +10148,31 @@
       <c r="S93" t="b">
         <v>1</v>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="T93" t="b">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U93" t="n">
+      <c r="Z93" t="n">
         <v>0.1665899197511018</v>
       </c>
     </row>
@@ -8474,12 +10252,31 @@
       <c r="S94" t="b">
         <v>1</v>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="T94" t="b">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U94" t="n">
+      <c r="Z94" t="n">
         <v>0.8106186578673872</v>
       </c>
     </row>
@@ -8559,12 +10356,31 @@
       <c r="S95" t="b">
         <v>0</v>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="T95" t="b">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y95" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U95" t="n">
+      <c r="Z95" t="n">
         <v>0.1340946844790925</v>
       </c>
     </row>
@@ -8644,12 +10460,31 @@
       <c r="S96" t="b">
         <v>1</v>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="T96" t="b">
+        <v>1</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U96" t="n">
+      <c r="Z96" t="n">
         <v>0.3675720314392596</v>
       </c>
     </row>
@@ -8729,12 +10564,31 @@
       <c r="S97" t="b">
         <v>1</v>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="T97" t="b">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U97" t="n">
+      <c r="Z97" t="n">
         <v>0.09282694409370729</v>
       </c>
     </row>
@@ -8814,12 +10668,31 @@
       <c r="S98" t="b">
         <v>0</v>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T98" t="b">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y98" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U98" t="n">
+      <c r="Z98" t="n">
         <v>-0.1641041287520223</v>
       </c>
     </row>
@@ -8899,12 +10772,31 @@
       <c r="S99" t="b">
         <v>1</v>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="T99" t="b">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U99" t="n">
+      <c r="Z99" t="n">
         <v>0.1181778409738131</v>
       </c>
     </row>
@@ -8984,12 +10876,31 @@
       <c r="S100" t="b">
         <v>1</v>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="T100" t="b">
+        <v>1</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U100" t="n">
+      <c r="Z100" t="n">
         <v>0.8522694603224307</v>
       </c>
     </row>
@@ -9069,12 +10980,31 @@
       <c r="S101" t="b">
         <v>1</v>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="T101" t="b">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U101" t="n">
+      <c r="Z101" t="n">
         <v>0.04606660828163711</v>
       </c>
     </row>
@@ -9154,12 +11084,31 @@
       <c r="S102" t="b">
         <v>0</v>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="T102" t="b">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y102" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U102" t="n">
+      <c r="Z102" t="n">
         <v>0.6342563076372758</v>
       </c>
     </row>
@@ -9239,12 +11188,31 @@
       <c r="S103" t="b">
         <v>0</v>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="T103" t="b">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y103" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U103" t="n">
+      <c r="Z103" t="n">
         <v>-0.04868293591860784</v>
       </c>
     </row>
@@ -9324,12 +11292,31 @@
       <c r="S104" t="b">
         <v>0</v>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T104" t="b">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y104" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U104" t="n">
+      <c r="Z104" t="n">
         <v>0.5274384209598384</v>
       </c>
     </row>
@@ -9409,12 +11396,31 @@
       <c r="S105" t="b">
         <v>1</v>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T105" t="b">
+        <v>1</v>
+      </c>
+      <c r="U105" t="n">
+        <v>1</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U105" t="n">
+      <c r="Z105" t="n">
         <v>0.283477625216312</v>
       </c>
     </row>
@@ -9494,12 +11500,31 @@
       <c r="S106" t="b">
         <v>1</v>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="T106" t="b">
+        <v>1</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1</v>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U106" t="n">
+      <c r="Z106" t="n">
         <v>0.8007900602856728</v>
       </c>
     </row>
@@ -9579,12 +11604,31 @@
       <c r="S107" t="b">
         <v>1</v>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="T107" t="b">
+        <v>1</v>
+      </c>
+      <c r="U107" t="n">
+        <v>1</v>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U107" t="n">
+      <c r="Z107" t="n">
         <v>0.2325161909364036</v>
       </c>
     </row>
@@ -9664,12 +11708,31 @@
       <c r="S108" t="b">
         <v>1</v>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="T108" t="b">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U108" t="n">
+      <c r="Z108" t="n">
         <v>0.5173971299593161</v>
       </c>
     </row>
@@ -9749,12 +11812,31 @@
       <c r="S109" t="b">
         <v>1</v>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="T109" t="b">
+        <v>1</v>
+      </c>
+      <c r="U109" t="n">
+        <v>1</v>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U109" t="n">
+      <c r="Z109" t="n">
         <v>0.1449447561492833</v>
       </c>
     </row>
@@ -9834,12 +11916,31 @@
       <c r="S110" t="b">
         <v>0</v>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="T110" t="b">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X110" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y110" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U110" t="n">
+      <c r="Z110" t="n">
         <v>-0.01660702160631289</v>
       </c>
     </row>
@@ -9919,12 +12020,31 @@
       <c r="S111" t="b">
         <v>0</v>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="T111" t="b">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y111" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U111" t="n">
+      <c r="Z111" t="n">
         <v>-0.01786015050138567</v>
       </c>
     </row>
@@ -10004,12 +12124,31 @@
       <c r="S112" t="b">
         <v>0</v>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="T112" t="b">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U112" t="n">
+      <c r="Z112" t="n">
         <v>-0.5053606587459023</v>
       </c>
     </row>
@@ -10089,12 +12228,31 @@
       <c r="S113" t="b">
         <v>0</v>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="T113" t="b">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y113" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U113" t="n">
+      <c r="Z113" t="n">
         <v>-0.6205497152332027</v>
       </c>
     </row>
@@ -10174,12 +12332,31 @@
       <c r="S114" t="b">
         <v>0</v>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="T114" t="b">
+        <v>1</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U114" t="n">
+      <c r="Z114" t="n">
         <v>0.08750463881458648</v>
       </c>
     </row>
@@ -10259,12 +12436,31 @@
       <c r="S115" t="b">
         <v>0</v>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="T115" t="b">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X115" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y115" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U115" t="n">
+      <c r="Z115" t="n">
         <v>-0.1095150245778216</v>
       </c>
     </row>
@@ -10344,12 +12540,31 @@
       <c r="S116" t="b">
         <v>1</v>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="T116" t="b">
+        <v>1</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U116" t="n">
+      <c r="Z116" t="n">
         <v>0.9109219056898333</v>
       </c>
     </row>
@@ -10429,12 +12644,31 @@
       <c r="S117" t="b">
         <v>1</v>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="T117" t="b">
+        <v>1</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U117" t="n">
+      <c r="Z117" t="n">
         <v>0.1287910202406055</v>
       </c>
     </row>
@@ -10514,12 +12748,31 @@
       <c r="S118" t="b">
         <v>1</v>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="T118" t="b">
+        <v>1</v>
+      </c>
+      <c r="U118" t="n">
+        <v>1</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U118" t="n">
+      <c r="Z118" t="n">
         <v>0.4030394862762469</v>
       </c>
     </row>
@@ -10599,12 +12852,31 @@
       <c r="S119" t="b">
         <v>1</v>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="T119" t="b">
+        <v>1</v>
+      </c>
+      <c r="U119" t="n">
+        <v>1</v>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U119" t="n">
+      <c r="Z119" t="n">
         <v>0.842516894295696</v>
       </c>
     </row>
@@ -10684,12 +12956,31 @@
       <c r="S120" t="b">
         <v>1</v>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="T120" t="b">
+        <v>1</v>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U120" t="n">
+      <c r="Z120" t="n">
         <v>0.831131552774762</v>
       </c>
     </row>
@@ -10769,12 +13060,31 @@
       <c r="S121" t="b">
         <v>0</v>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="T121" t="b">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y121" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U121" t="n">
+      <c r="Z121" t="n">
         <v>-0.01065871435132504</v>
       </c>
     </row>
@@ -10850,12 +13160,31 @@
       <c r="S122" t="b">
         <v>1</v>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="T122" t="b">
+        <v>1</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1</v>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U122" t="n">
+      <c r="Z122" t="n">
         <v>0.1053921764885984</v>
       </c>
     </row>
@@ -10931,12 +13260,31 @@
       <c r="S123" t="b">
         <v>0</v>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="T123" t="b">
+        <v>1</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y123" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U123" t="n">
+      <c r="Z123" t="n">
         <v>0.1180058943928919</v>
       </c>
     </row>
@@ -11012,12 +13360,31 @@
       <c r="S124" t="b">
         <v>1</v>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="T124" t="b">
+        <v>1</v>
+      </c>
+      <c r="U124" t="n">
+        <v>1</v>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U124" t="n">
+      <c r="Z124" t="n">
         <v>0.08503427417927933</v>
       </c>
     </row>
@@ -11093,12 +13460,31 @@
       <c r="S125" t="b">
         <v>0</v>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="T125" t="b">
+        <v>1</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y125" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U125" t="n">
+      <c r="Z125" t="n">
         <v>0.3362065492331775</v>
       </c>
     </row>
@@ -11174,12 +13560,31 @@
       <c r="S126" t="b">
         <v>1</v>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="T126" t="b">
+        <v>1</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U126" t="n">
+      <c r="Z126" t="n">
         <v>0.2925514080494576</v>
       </c>
     </row>
@@ -11255,12 +13660,31 @@
       <c r="S127" t="b">
         <v>0</v>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="T127" t="b">
+        <v>1</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y127" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U127" t="n">
+      <c r="Z127" t="n">
         <v>0.0270242036223991</v>
       </c>
     </row>
@@ -11336,12 +13760,31 @@
       <c r="S128" t="b">
         <v>0</v>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="T128" t="b">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X128" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y128" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U128" t="n">
+      <c r="Z128" t="n">
         <v>-0.3199898702741562</v>
       </c>
     </row>
@@ -11417,12 +13860,31 @@
       <c r="S129" t="b">
         <v>1</v>
       </c>
-      <c r="T129" t="inlineStr">
+      <c r="T129" t="b">
+        <v>1</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U129" t="n">
+      <c r="Z129" t="n">
         <v>0.09476342247097236</v>
       </c>
     </row>
@@ -11498,12 +13960,31 @@
       <c r="S130" t="b">
         <v>1</v>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="T130" t="b">
+        <v>1</v>
+      </c>
+      <c r="U130" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U130" t="n">
+      <c r="Z130" t="n">
         <v>0.6571438954610531</v>
       </c>
     </row>
@@ -11579,12 +14060,31 @@
       <c r="S131" t="b">
         <v>1</v>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="T131" t="b">
+        <v>1</v>
+      </c>
+      <c r="U131" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U131" t="n">
+      <c r="Z131" t="n">
         <v>0.6252537434586177</v>
       </c>
     </row>
@@ -11660,12 +14160,31 @@
       <c r="S132" t="b">
         <v>1</v>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="T132" t="b">
+        <v>1</v>
+      </c>
+      <c r="U132" t="n">
+        <v>1</v>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U132" t="n">
+      <c r="Z132" t="n">
         <v>0.7095795597442676</v>
       </c>
     </row>
@@ -11741,12 +14260,31 @@
       <c r="S133" t="b">
         <v>1</v>
       </c>
-      <c r="T133" t="inlineStr">
+      <c r="T133" t="b">
+        <v>1</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U133" t="n">
+      <c r="Z133" t="n">
         <v>0.02841031963523866</v>
       </c>
     </row>
@@ -11822,12 +14360,31 @@
       <c r="S134" t="b">
         <v>0</v>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="T134" t="b">
+        <v>1</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y134" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U134" t="n">
+      <c r="Z134" t="n">
         <v>0.2438246785821788</v>
       </c>
     </row>
@@ -11903,12 +14460,31 @@
       <c r="S135" t="b">
         <v>1</v>
       </c>
-      <c r="T135" t="inlineStr">
+      <c r="T135" t="b">
+        <v>1</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U135" t="n">
+      <c r="Z135" t="n">
         <v>0.07242290316719979</v>
       </c>
     </row>
@@ -11984,12 +14560,31 @@
       <c r="S136" t="b">
         <v>1</v>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="T136" t="b">
+        <v>1</v>
+      </c>
+      <c r="U136" t="n">
+        <v>1</v>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U136" t="n">
+      <c r="Z136" t="n">
         <v>0.14030568898474</v>
       </c>
     </row>
@@ -12065,12 +14660,31 @@
       <c r="S137" t="b">
         <v>1</v>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="T137" t="b">
+        <v>1</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1</v>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U137" t="n">
+      <c r="Z137" t="n">
         <v>0.1507821149997631</v>
       </c>
     </row>
@@ -12146,12 +14760,31 @@
       <c r="S138" t="b">
         <v>1</v>
       </c>
-      <c r="T138" t="inlineStr">
+      <c r="T138" t="b">
+        <v>1</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1</v>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U138" t="n">
+      <c r="Z138" t="n">
         <v>0.1113210754205208</v>
       </c>
     </row>
@@ -12227,12 +14860,31 @@
       <c r="S139" t="b">
         <v>1</v>
       </c>
-      <c r="T139" t="inlineStr">
+      <c r="T139" t="b">
+        <v>1</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1</v>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U139" t="n">
+      <c r="Z139" t="n">
         <v>0.07434793824180397</v>
       </c>
     </row>
@@ -12308,12 +14960,31 @@
       <c r="S140" t="b">
         <v>1</v>
       </c>
-      <c r="T140" t="inlineStr">
+      <c r="T140" t="b">
+        <v>1</v>
+      </c>
+      <c r="U140" t="n">
+        <v>1</v>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U140" t="n">
+      <c r="Z140" t="n">
         <v>0.7092139921510048</v>
       </c>
     </row>
@@ -12389,12 +15060,31 @@
       <c r="S141" t="b">
         <v>0</v>
       </c>
-      <c r="T141" t="inlineStr">
+      <c r="T141" t="b">
+        <v>1</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y141" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U141" t="n">
+      <c r="Z141" t="n">
         <v>0.1231999685147961</v>
       </c>
     </row>
@@ -12470,12 +15160,31 @@
       <c r="S142" t="b">
         <v>1</v>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="T142" t="b">
+        <v>1</v>
+      </c>
+      <c r="U142" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U142" t="n">
+      <c r="Z142" t="n">
         <v>0.7951963273037072</v>
       </c>
     </row>
@@ -12551,12 +15260,31 @@
       <c r="S143" t="b">
         <v>0</v>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="T143" t="b">
+        <v>1</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y143" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U143" t="n">
+      <c r="Z143" t="n">
         <v>0.2258012935990694</v>
       </c>
     </row>
@@ -12632,12 +15360,31 @@
       <c r="S144" t="b">
         <v>1</v>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="T144" t="b">
+        <v>1</v>
+      </c>
+      <c r="U144" t="n">
+        <v>1</v>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U144" t="n">
+      <c r="Z144" t="n">
         <v>0.5511044361993358</v>
       </c>
     </row>
@@ -12713,12 +15460,31 @@
       <c r="S145" t="b">
         <v>0</v>
       </c>
-      <c r="T145" t="inlineStr">
+      <c r="T145" t="b">
+        <v>1</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y145" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U145" t="n">
+      <c r="Z145" t="n">
         <v>0.001368747030121686</v>
       </c>
     </row>
@@ -12794,12 +15560,31 @@
       <c r="S146" t="b">
         <v>1</v>
       </c>
-      <c r="T146" t="inlineStr">
+      <c r="T146" t="b">
+        <v>1</v>
+      </c>
+      <c r="U146" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U146" t="n">
+      <c r="Z146" t="n">
         <v>0.201225524984275</v>
       </c>
     </row>
@@ -12875,12 +15660,31 @@
       <c r="S147" t="b">
         <v>1</v>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="T147" t="b">
+        <v>1</v>
+      </c>
+      <c r="U147" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U147" t="n">
+      <c r="Z147" t="n">
         <v>0.04339926493096158</v>
       </c>
     </row>
@@ -12956,12 +15760,31 @@
       <c r="S148" t="b">
         <v>1</v>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="T148" t="b">
+        <v>1</v>
+      </c>
+      <c r="U148" t="n">
+        <v>1</v>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U148" t="n">
+      <c r="Z148" t="n">
         <v>0.6886593450953726</v>
       </c>
     </row>
@@ -13037,12 +15860,31 @@
       <c r="S149" t="b">
         <v>0</v>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="T149" t="b">
+        <v>1</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X149" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y149" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U149" t="n">
+      <c r="Z149" t="n">
         <v>0.03474365755682907</v>
       </c>
     </row>
@@ -13118,12 +15960,31 @@
       <c r="S150" t="b">
         <v>1</v>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="T150" t="b">
+        <v>1</v>
+      </c>
+      <c r="U150" t="n">
+        <v>1</v>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U150" t="n">
+      <c r="Z150" t="n">
         <v>0.3721825118308238</v>
       </c>
     </row>
@@ -13199,12 +16060,31 @@
       <c r="S151" t="b">
         <v>1</v>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="T151" t="b">
+        <v>1</v>
+      </c>
+      <c r="U151" t="n">
+        <v>1</v>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U151" t="n">
+      <c r="Z151" t="n">
         <v>0.04530063250284944</v>
       </c>
     </row>
@@ -13280,12 +16160,31 @@
       <c r="S152" t="b">
         <v>0</v>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="T152" t="b">
+        <v>1</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X152" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y152" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U152" t="n">
+      <c r="Z152" t="n">
         <v>0.01098462569029188</v>
       </c>
     </row>
@@ -13361,12 +16260,31 @@
       <c r="S153" t="b">
         <v>1</v>
       </c>
-      <c r="T153" t="inlineStr">
+      <c r="T153" t="b">
+        <v>1</v>
+      </c>
+      <c r="U153" t="n">
+        <v>1</v>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U153" t="n">
+      <c r="Z153" t="n">
         <v>0.2085508344622853</v>
       </c>
     </row>
@@ -13442,12 +16360,31 @@
       <c r="S154" t="b">
         <v>1</v>
       </c>
-      <c r="T154" t="inlineStr">
+      <c r="T154" t="b">
+        <v>1</v>
+      </c>
+      <c r="U154" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U154" t="n">
+      <c r="Z154" t="n">
         <v>0.4777014185237922</v>
       </c>
     </row>
@@ -13523,12 +16460,31 @@
       <c r="S155" t="b">
         <v>0</v>
       </c>
-      <c r="T155" t="inlineStr">
+      <c r="T155" t="b">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y155" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U155" t="n">
+      <c r="Z155" t="n">
         <v>-0.02375540358957351</v>
       </c>
     </row>
@@ -13604,12 +16560,31 @@
       <c r="S156" t="b">
         <v>1</v>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="T156" t="b">
+        <v>1</v>
+      </c>
+      <c r="U156" t="n">
+        <v>1</v>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U156" t="n">
+      <c r="Z156" t="n">
         <v>0.7516239665782835</v>
       </c>
     </row>
@@ -13685,12 +16660,31 @@
       <c r="S157" t="b">
         <v>1</v>
       </c>
-      <c r="T157" t="inlineStr">
+      <c r="T157" t="b">
+        <v>1</v>
+      </c>
+      <c r="U157" t="n">
+        <v>1</v>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U157" t="n">
+      <c r="Z157" t="n">
         <v>0.07285283807874599</v>
       </c>
     </row>
@@ -13766,12 +16760,31 @@
       <c r="S158" t="b">
         <v>0</v>
       </c>
-      <c r="T158" t="inlineStr">
+      <c r="T158" t="b">
+        <v>1</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X158" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y158" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U158" t="n">
+      <c r="Z158" t="n">
         <v>0.1517857348303586</v>
       </c>
     </row>
@@ -13847,12 +16860,31 @@
       <c r="S159" t="b">
         <v>0</v>
       </c>
-      <c r="T159" t="inlineStr">
+      <c r="T159" t="b">
+        <v>1</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X159" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y159" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U159" t="n">
+      <c r="Z159" t="n">
         <v>0.007427959038588727</v>
       </c>
     </row>
@@ -13928,12 +16960,31 @@
       <c r="S160" t="b">
         <v>1</v>
       </c>
-      <c r="T160" t="inlineStr">
+      <c r="T160" t="b">
+        <v>1</v>
+      </c>
+      <c r="U160" t="n">
+        <v>1</v>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y160" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U160" t="n">
+      <c r="Z160" t="n">
         <v>0.5566097705520651</v>
       </c>
     </row>
@@ -14009,12 +17060,31 @@
       <c r="S161" t="b">
         <v>0</v>
       </c>
-      <c r="T161" t="inlineStr">
+      <c r="T161" t="b">
+        <v>0</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X161" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y161" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U161" t="n">
+      <c r="Z161" t="n">
         <v>0.01908756799099964</v>
       </c>
     </row>
@@ -14090,12 +17160,31 @@
       <c r="S162" t="b">
         <v>1</v>
       </c>
-      <c r="T162" t="inlineStr">
+      <c r="T162" t="b">
+        <v>1</v>
+      </c>
+      <c r="U162" t="n">
+        <v>1</v>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U162" t="n">
+      <c r="Z162" t="n">
         <v>0.4775528490734883</v>
       </c>
     </row>
@@ -14171,12 +17260,31 @@
       <c r="S163" t="b">
         <v>0</v>
       </c>
-      <c r="T163" t="inlineStr">
+      <c r="T163" t="b">
+        <v>1</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X163" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y163" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U163" t="n">
+      <c r="Z163" t="n">
         <v>0.07691549901010986</v>
       </c>
     </row>
@@ -14252,12 +17360,31 @@
       <c r="S164" t="b">
         <v>0</v>
       </c>
-      <c r="T164" t="inlineStr">
+      <c r="T164" t="b">
+        <v>1</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X164" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y164" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U164" t="n">
+      <c r="Z164" t="n">
         <v>0.4575248014203314</v>
       </c>
     </row>
@@ -14333,12 +17460,31 @@
       <c r="S165" t="b">
         <v>1</v>
       </c>
-      <c r="T165" t="inlineStr">
+      <c r="T165" t="b">
+        <v>1</v>
+      </c>
+      <c r="U165" t="n">
+        <v>1</v>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U165" t="n">
+      <c r="Z165" t="n">
         <v>0.07398010268228294</v>
       </c>
     </row>
@@ -14414,12 +17560,31 @@
       <c r="S166" t="b">
         <v>1</v>
       </c>
-      <c r="T166" t="inlineStr">
+      <c r="T166" t="b">
+        <v>1</v>
+      </c>
+      <c r="U166" t="n">
+        <v>1</v>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U166" t="n">
+      <c r="Z166" t="n">
         <v>0.7527074933735513</v>
       </c>
     </row>
@@ -14495,12 +17660,31 @@
       <c r="S167" t="b">
         <v>1</v>
       </c>
-      <c r="T167" t="inlineStr">
+      <c r="T167" t="b">
+        <v>1</v>
+      </c>
+      <c r="U167" t="n">
+        <v>1</v>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U167" t="n">
+      <c r="Z167" t="n">
         <v>0.05164286164633303</v>
       </c>
     </row>
@@ -14576,12 +17760,31 @@
       <c r="S168" t="b">
         <v>0</v>
       </c>
-      <c r="T168" t="inlineStr">
+      <c r="T168" t="b">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X168" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y168" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U168" t="n">
+      <c r="Z168" t="n">
         <v>-0.09089012242808436</v>
       </c>
     </row>
@@ -14657,12 +17860,31 @@
       <c r="S169" t="b">
         <v>0</v>
       </c>
-      <c r="T169" t="inlineStr">
+      <c r="T169" t="b">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X169" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y169" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U169" t="n">
+      <c r="Z169" t="n">
         <v>-0.01412788508008611</v>
       </c>
     </row>
@@ -14738,12 +17960,31 @@
       <c r="S170" t="b">
         <v>1</v>
       </c>
-      <c r="T170" t="inlineStr">
+      <c r="T170" t="b">
+        <v>1</v>
+      </c>
+      <c r="U170" t="n">
+        <v>1</v>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U170" t="n">
+      <c r="Z170" t="n">
         <v>0.03446660173359506</v>
       </c>
     </row>
@@ -14819,12 +18060,31 @@
       <c r="S171" t="b">
         <v>0</v>
       </c>
-      <c r="T171" t="inlineStr">
+      <c r="T171" t="b">
+        <v>1</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X171" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y171" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U171" t="n">
+      <c r="Z171" t="n">
         <v>0.001700562724399446</v>
       </c>
     </row>
@@ -14900,12 +18160,31 @@
       <c r="S172" t="b">
         <v>0</v>
       </c>
-      <c r="T172" t="inlineStr">
+      <c r="T172" t="b">
+        <v>1</v>
+      </c>
+      <c r="U172" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X172" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y172" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U172" t="n">
+      <c r="Z172" t="n">
         <v>0.07639654678320174</v>
       </c>
     </row>
@@ -14981,12 +18260,31 @@
       <c r="S173" t="b">
         <v>0</v>
       </c>
-      <c r="T173" t="inlineStr">
+      <c r="T173" t="b">
+        <v>0</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X173" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y173" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U173" t="n">
+      <c r="Z173" t="n">
         <v>-0.1424635703629356</v>
       </c>
     </row>
@@ -15062,12 +18360,31 @@
       <c r="S174" t="b">
         <v>0</v>
       </c>
-      <c r="T174" t="inlineStr">
+      <c r="T174" t="b">
+        <v>1</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X174" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y174" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U174" t="n">
+      <c r="Z174" t="n">
         <v>0.05328899780643648</v>
       </c>
     </row>
@@ -15143,12 +18460,31 @@
       <c r="S175" t="b">
         <v>1</v>
       </c>
-      <c r="T175" t="inlineStr">
+      <c r="T175" t="b">
+        <v>1</v>
+      </c>
+      <c r="U175" t="n">
+        <v>1</v>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U175" t="n">
+      <c r="Z175" t="n">
         <v>0.02212962973313493</v>
       </c>
     </row>
@@ -15224,12 +18560,31 @@
       <c r="S176" t="b">
         <v>0</v>
       </c>
-      <c r="T176" t="inlineStr">
+      <c r="T176" t="b">
+        <v>1</v>
+      </c>
+      <c r="U176" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X176" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y176" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U176" t="n">
+      <c r="Z176" t="n">
         <v>0.03010936816724678</v>
       </c>
     </row>
@@ -15305,12 +18660,31 @@
       <c r="S177" t="b">
         <v>1</v>
       </c>
-      <c r="T177" t="inlineStr">
+      <c r="T177" t="b">
+        <v>1</v>
+      </c>
+      <c r="U177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y177" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U177" t="n">
+      <c r="Z177" t="n">
         <v>0.1431857618205983</v>
       </c>
     </row>
@@ -15386,12 +18760,31 @@
       <c r="S178" t="b">
         <v>1</v>
       </c>
-      <c r="T178" t="inlineStr">
+      <c r="T178" t="b">
+        <v>1</v>
+      </c>
+      <c r="U178" t="n">
+        <v>1</v>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y178" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U178" t="n">
+      <c r="Z178" t="n">
         <v>0.5585827107826618</v>
       </c>
     </row>
@@ -15467,12 +18860,31 @@
       <c r="S179" t="b">
         <v>1</v>
       </c>
-      <c r="T179" t="inlineStr">
+      <c r="T179" t="b">
+        <v>1</v>
+      </c>
+      <c r="U179" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y179" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U179" t="n">
+      <c r="Z179" t="n">
         <v>0.7925062061473596</v>
       </c>
     </row>
@@ -15548,12 +18960,31 @@
       <c r="S180" t="b">
         <v>1</v>
       </c>
-      <c r="T180" t="inlineStr">
+      <c r="T180" t="b">
+        <v>1</v>
+      </c>
+      <c r="U180" t="n">
+        <v>1</v>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="X180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y180" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U180" t="n">
+      <c r="Z180" t="n">
         <v>0.7317004821564427</v>
       </c>
     </row>
@@ -15629,17 +19060,36 @@
       <c r="S181" t="b">
         <v>1</v>
       </c>
-      <c r="T181" t="inlineStr">
+      <c r="T181" t="b">
+        <v>1</v>
+      </c>
+      <c r="U181" t="n">
+        <v>1</v>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="X181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" t="inlineStr">
         <is>
           <t>Q_rep_injected_minus_paired_baseline</t>
         </is>
       </c>
-      <c r="U181" t="n">
+      <c r="Z181" t="n">
         <v>0.001639426361507046</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U181"/>
+  <autoFilter ref="A1:Z181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33959,7 +37409,7 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
@@ -33998,7 +37448,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>241.7737677999539</v>
+        <v>59.98775969999951</v>
       </c>
       <c r="B2" t="n">
         <v>180</v>
@@ -34007,7 +37457,7 @@
         <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>2.233492806525334</v>
+        <v>9.001835744363465</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
